--- a/Artikelnummer.xlsx
+++ b/Artikelnummer.xlsx
@@ -1,20 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10605"/>
   <workbookPr showInkAnnotation="0" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://willistober-my.sharepoint.com/personal/m_gerdau_stober-online_de/Documents/Konfigurator/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/var/mobile/Containers/Data/Application/E4572EA0-0BAD-4B80-AE01-7E3DB6FFD8F2/Library/Application Support/Drafts/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{DF8D276C-7938-418F-8A39-7ADA295FDD50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F6149563-7CD6-FD49-8259-313BEE1AC47D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="1620" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="0" windowHeight="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
-    <sheet name="Tabelle2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -37,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="38">
   <si>
     <t>Kategorie</t>
   </si>
@@ -93,9 +92,18 @@
     <t>Akkupack</t>
   </si>
   <si>
+    <t>GS</t>
+  </si>
+  <si>
     <t>Full Energy</t>
   </si>
   <si>
+    <t>UGC Full</t>
+  </si>
+  <si>
+    <t>UGC Fire</t>
+  </si>
+  <si>
     <t>Betriebsrat &amp; Energie</t>
   </si>
   <si>
@@ -111,103 +119,50 @@
     <t>BS ziehend</t>
   </si>
   <si>
+    <t>DK_ED1</t>
+  </si>
+  <si>
+    <t>DK_ED2</t>
+  </si>
+  <si>
     <t>BEA Eagle Artec</t>
   </si>
   <si>
+    <t>BEA Flatscan</t>
+  </si>
+  <si>
     <t>BEA Flatscan 3D</t>
   </si>
   <si>
+    <t>BEA IRS4</t>
+  </si>
+  <si>
     <t>Flächentaster AP</t>
   </si>
   <si>
     <t>Schlüsselschalter AP</t>
   </si>
   <si>
+    <t>Gestänge</t>
+  </si>
+  <si>
     <t>MotionIQ aktiv</t>
   </si>
   <si>
     <t>DK_M_A01</t>
-  </si>
-  <si>
-    <t>10176432  </t>
-  </si>
-  <si>
-    <t>10805080 </t>
-  </si>
-  <si>
-    <t>10513882                                        Ed100</t>
-  </si>
-  <si>
-    <t>10513889                                        Ed250</t>
-  </si>
-  <si>
-    <t>10513893                                        Gleitschiene</t>
-  </si>
-  <si>
-    <t>10176432                                        Gestänge f.Sturztiefe von 0 bis 225mm</t>
-  </si>
-  <si>
-    <t>10176431                                          Gestänge f.Sturztiefe von 225 bis 500mm</t>
-  </si>
-  <si>
-    <t>10385422                                        Upgradecard Full Energy für Ed100</t>
-  </si>
-  <si>
-    <t>Kein angelegter Artikel            Upgradecard Brandschutzfür Ed100</t>
-  </si>
-  <si>
-    <t>10385423                                        Upgradecard Full Energy für Ed250</t>
-  </si>
-  <si>
-    <t>10385421                                        Upgradecard Brandschutzfür Ed250</t>
-  </si>
-  <si>
-    <t>10282489                                       Sensorleiste irs4 L 1200mm</t>
-  </si>
-  <si>
-    <t>10282490                                          dto 1600mm</t>
-  </si>
-  <si>
-    <t>10467968                                       Flatscan silber</t>
-  </si>
-  <si>
-    <t>10805080                                          Flatscan schwarz</t>
-  </si>
-  <si>
-    <t>Kein angelegter Artikel            Flatscan 3D</t>
-  </si>
-  <si>
-    <t>10408635                                        Verkleidung Basic</t>
-  </si>
-  <si>
-    <t>10467971                                        Verkleidung RM</t>
-  </si>
-  <si>
-    <t>10529214                                       Schlißfolgeregelung ESR</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Inherit"/>
     </font>
   </fonts>
   <fills count="2">
@@ -230,15 +185,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -554,300 +502,201 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0DDFD00C-6FF9-2B49-B677-F644D7C4DC40}">
   <dimension ref="A1:C17"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="23.21875" customWidth="1"/>
-    <col min="2" max="2" width="15.21875" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="23.26953125" customWidth="1"/>
+    <col min="2" max="2" width="15.19921875" customWidth="1"/>
+    <col min="3" max="3" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>14</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
       </c>
-      <c r="C2" s="1">
-        <v>10513882</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+      <c r="C2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
       </c>
-      <c r="C3" s="1">
-        <v>10513889</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
       </c>
-      <c r="C4" s="1">
-        <v>10282489</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+      <c r="C4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>15</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+      <c r="C5" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>15</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
       </c>
-      <c r="C6" s="1" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+      <c r="C6" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>16</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="1" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+      <c r="C7" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>16</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+      <c r="C8" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>16</v>
       </c>
       <c r="B9" t="s">
         <v>10</v>
       </c>
-      <c r="C9" s="1" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+      <c r="C9" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="1" t="s">
+      <c r="C10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>36</v>
+      </c>
+      <c r="C11" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A12" t="s">
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>22</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="13" spans="1:3">
+        <v>25</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>13</v>
       </c>
       <c r="B13" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="1">
-        <v>10513893</v>
-      </c>
-    </row>
-    <row r="14" spans="1:3">
+        <v>26</v>
+      </c>
+      <c r="C13" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>13</v>
       </c>
       <c r="B14" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="1" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="15" spans="1:3">
+      <c r="C14" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A15" t="s">
+        <v>22</v>
+      </c>
+      <c r="B15" t="s">
         <v>19</v>
       </c>
-      <c r="B15" t="s">
-        <v>18</v>
-      </c>
-      <c r="C15" s="1">
-        <v>10385423</v>
-      </c>
-    </row>
-    <row r="16" spans="1:3">
+      <c r="C15" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A16" t="s">
         <v>14</v>
       </c>
       <c r="B16" t="s">
-        <v>20</v>
-      </c>
-      <c r="C16" s="1">
-        <v>10385421</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3">
+        <v>23</v>
+      </c>
+      <c r="C16" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A17" t="s">
         <v>14</v>
       </c>
       <c r="B17" t="s">
+        <v>24</v>
+      </c>
+      <c r="C17" t="s">
         <v>21</v>
-      </c>
-      <c r="C17" s="1">
-        <v>10385421</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{21701C42-EF19-4AF4-81CD-78BC55F58960}">
-  <dimension ref="A1:A17"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4"/>
-  <cols>
-    <col min="1" max="1" width="97.33203125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1" ht="15.6">
-      <c r="A1" s="2" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1" ht="15.6">
-      <c r="A2" s="2" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" ht="15.6">
-      <c r="A3" s="2" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1" ht="15.6">
-      <c r="A4" s="2" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5" s="3" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1" ht="15.6">
-      <c r="A6" s="2" t="s">
-        <v>37</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" ht="15.6">
-      <c r="A7" s="2" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1" ht="15.6">
-      <c r="A8" s="2" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="9" spans="1:1" ht="15.6">
-      <c r="A9" s="2" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="10" spans="1:1" ht="15.6">
-      <c r="A10" s="2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:1">
-      <c r="A11" s="3" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="12" spans="1:1" ht="15.6">
-      <c r="A12" s="2" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="13" spans="1:1">
-      <c r="A13" s="3" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="14" spans="1:1" ht="15.6">
-      <c r="A14" s="2" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="15" spans="1:1" ht="15.6">
-      <c r="A15" s="2" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="16" spans="1:1" ht="15.6">
-      <c r="A16" s="2" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:1" ht="15.6">
-      <c r="A17" s="2" t="s">
-        <v>48</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
 </file>